--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137042120</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137042140</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>137042251</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>137042507</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137042057</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>137042285</v>
       </c>
       <c r="B9" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137042120</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137042140</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>137042251</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>137042507</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137042057</v>
       </c>
       <c r="B8" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>137042285</v>
       </c>
       <c r="B9" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137041959</v>
       </c>
       <c r="B10" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>137042183</v>
       </c>
       <c r="B11" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>137042490</v>
       </c>
       <c r="B12" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>137042499</v>
       </c>
       <c r="B13" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -923,11 +923,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1033,11 +1029,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1143,11 +1135,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,11 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1363,11 +1347,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1473,11 +1453,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1584,11 +1560,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1696,11 +1668,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1808,11 +1776,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1920,11 +1884,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137042120</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137042140</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137042251</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137042507</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137042057</v>
       </c>
       <c r="B8" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137042285</v>
       </c>
       <c r="B9" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>137041959</v>
       </c>
       <c r="B10" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>137042183</v>
       </c>
       <c r="B11" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>137042490</v>
       </c>
       <c r="B12" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137042499</v>
       </c>
       <c r="B13" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137042120</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137042140</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137042251</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137042507</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137042057</v>
       </c>
       <c r="B8" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137042285</v>
       </c>
       <c r="B9" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137042120</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137042140</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137042251</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137042507</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137042057</v>
       </c>
       <c r="B8" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137042285</v>
       </c>
       <c r="B9" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37482-2026 artfynd.xlsx
+++ b/artfynd/A 37482-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137042267</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137042292</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137042120</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137042140</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137042251</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137042507</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137042057</v>
       </c>
       <c r="B8" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137042285</v>
       </c>
       <c r="B9" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
